--- a/pandas/Filesave.xlsx
+++ b/pandas/Filesave.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Sumaiya Rani</t>
         </is>
       </c>
       <c r="C3" t="n">
